--- a/database/event/6861/event_6861_evp_summary.xlsx
+++ b/database/event/6861/event_6861_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>7.7213</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3.2109</v>
       </c>
       <c r="D2" t="n">
         <v>2.6979</v>
@@ -545,7 +545,7 @@
         <v>7.4161</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3.084</v>
       </c>
       <c r="D3" t="n">
         <v>2.5746</v>
@@ -591,7 +591,7 @@
         <v>5.6316</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.3419</v>
       </c>
       <c r="D4" t="n">
         <v>1.8537</v>
@@ -637,7 +637,7 @@
         <v>4.8344</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.0104</v>
       </c>
       <c r="D5" t="n">
         <v>1.5316</v>
@@ -683,7 +683,7 @@
         <v>4.8181</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.0036</v>
       </c>
       <c r="D6" t="n">
         <v>1.525</v>
@@ -729,7 +729,7 @@
         <v>4.785</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.9898</v>
       </c>
       <c r="D7" t="n">
         <v>1.5117</v>
@@ -775,7 +775,7 @@
         <v>4.7623</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1.9804</v>
       </c>
       <c r="D8" t="n">
         <v>1.5025</v>
@@ -821,7 +821,7 @@
         <v>4.6624</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1.9389</v>
       </c>
       <c r="D9" t="n">
         <v>1.4621</v>
@@ -867,7 +867,7 @@
         <v>4.2131</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1.752</v>
       </c>
       <c r="D10" t="n">
         <v>1.2806</v>
@@ -913,7 +913,7 @@
         <v>3.6409</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.5141</v>
       </c>
       <c r="D11" t="n">
         <v>1.0495</v>
@@ -959,7 +959,7 @@
         <v>3.6122</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.5021</v>
       </c>
       <c r="D12" t="n">
         <v>1.0379</v>
@@ -1005,7 +1005,7 @@
         <v>3.5917</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.4936</v>
       </c>
       <c r="D13" t="n">
         <v>1.0296</v>
@@ -1051,7 +1051,7 @@
         <v>3.3281</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.384</v>
       </c>
       <c r="D14" t="n">
         <v>0.9231</v>
@@ -1097,7 +1097,7 @@
         <v>3.113</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.2945</v>
       </c>
       <c r="D15" t="n">
         <v>0.8362000000000001</v>
@@ -1143,7 +1143,7 @@
         <v>3.1101</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.2933</v>
       </c>
       <c r="D16" t="n">
         <v>0.835</v>
@@ -1189,7 +1189,7 @@
         <v>2.5503</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.0605</v>
       </c>
       <c r="D17" t="n">
         <v>0.6089</v>
@@ -1235,7 +1235,7 @@
         <v>2.3773</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.9886</v>
       </c>
       <c r="D18" t="n">
         <v>0.539</v>
@@ -1281,7 +1281,7 @@
         <v>2.3304</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.9691</v>
       </c>
       <c r="D19" t="n">
         <v>0.5201</v>
@@ -1327,7 +1327,7 @@
         <v>2.2313</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="D20" t="n">
         <v>0.48</v>
@@ -1373,7 +1373,7 @@
         <v>2.1796</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.9064</v>
       </c>
       <c r="D21" t="n">
         <v>0.4591</v>
@@ -1419,7 +1419,7 @@
         <v>2.1588</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="D22" t="n">
         <v>0.4507</v>
@@ -1465,7 +1465,7 @@
         <v>2.083</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.8662</v>
       </c>
       <c r="D23" t="n">
         <v>0.4201</v>
@@ -1511,7 +1511,7 @@
         <v>2.0321</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.8451</v>
       </c>
       <c r="D24" t="n">
         <v>0.3996</v>
@@ -1557,7 +1557,7 @@
         <v>1.9797</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.8233</v>
       </c>
       <c r="D25" t="n">
         <v>0.3784</v>
@@ -1603,7 +1603,7 @@
         <v>1.8752</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.7798</v>
       </c>
       <c r="D26" t="n">
         <v>0.3362</v>
@@ -1649,7 +1649,7 @@
         <v>1.7877</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="D27" t="n">
         <v>0.3008</v>
@@ -1695,7 +1695,7 @@
         <v>1.7245</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.7171</v>
       </c>
       <c r="D28" t="n">
         <v>0.2753</v>
@@ -1741,7 +1741,7 @@
         <v>1.6568</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="D29" t="n">
         <v>0.2479</v>
@@ -1787,7 +1787,7 @@
         <v>1.4771</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.6143</v>
       </c>
       <c r="D30" t="n">
         <v>0.1754</v>
@@ -1833,7 +1833,7 @@
         <v>1.2841</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.534</v>
       </c>
       <c r="D31" t="n">
         <v>0.0974</v>
@@ -1879,7 +1879,7 @@
         <v>1.2418</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.5164</v>
       </c>
       <c r="D32" t="n">
         <v>0.0803</v>
@@ -1925,7 +1925,7 @@
         <v>1.1082</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.4608</v>
       </c>
       <c r="D33" t="n">
         <v>0.0263</v>
@@ -1971,7 +1971,7 @@
         <v>0.9861</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.4101</v>
       </c>
       <c r="D34" t="n">
         <v>-0.023</v>
@@ -2017,7 +2017,7 @@
         <v>0.9725</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.4044</v>
       </c>
       <c r="D35" t="n">
         <v>-0.0285</v>
@@ -2063,7 +2063,7 @@
         <v>0.9663</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.4018</v>
       </c>
       <c r="D36" t="n">
         <v>-0.031</v>
@@ -2109,7 +2109,7 @@
         <v>0.8711</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.3622</v>
       </c>
       <c r="D37" t="n">
         <v>-0.06950000000000001</v>
@@ -2155,7 +2155,7 @@
         <v>0.5088</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.2116</v>
       </c>
       <c r="D38" t="n">
         <v>-0.2158</v>
@@ -2201,7 +2201,7 @@
         <v>0.5079</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.2112</v>
       </c>
       <c r="D39" t="n">
         <v>-0.2162</v>
@@ -2247,7 +2247,7 @@
         <v>0.4971</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.2067</v>
       </c>
       <c r="D40" t="n">
         <v>-0.2205</v>
@@ -2293,7 +2293,7 @@
         <v>0.4477</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.1862</v>
       </c>
       <c r="D41" t="n">
         <v>-0.2405</v>
@@ -2339,7 +2339,7 @@
         <v>0.3999</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.1663</v>
       </c>
       <c r="D42" t="n">
         <v>-0.2598</v>
@@ -2385,7 +2385,7 @@
         <v>0.2546</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.1059</v>
       </c>
       <c r="D43" t="n">
         <v>-0.3185</v>
@@ -2431,7 +2431,7 @@
         <v>0.2274</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.0946</v>
       </c>
       <c r="D44" t="n">
         <v>-0.3295</v>
@@ -2477,7 +2477,7 @@
         <v>0.2123</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.0883</v>
       </c>
       <c r="D45" t="n">
         <v>-0.3356</v>
@@ -2523,7 +2523,7 @@
         <v>0.2026</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.0843</v>
       </c>
       <c r="D46" t="n">
         <v>-0.3395</v>
@@ -2569,7 +2569,7 @@
         <v>-0.0382</v>
       </c>
       <c r="C47" t="n">
-        <v>-0</v>
+        <v>-0.0159</v>
       </c>
       <c r="D47" t="n">
         <v>-0.4368</v>
@@ -2615,7 +2615,7 @@
         <v>-0.1054</v>
       </c>
       <c r="C48" t="n">
-        <v>-0</v>
+        <v>-0.0438</v>
       </c>
       <c r="D48" t="n">
         <v>-0.4639</v>
@@ -2661,7 +2661,7 @@
         <v>-0.1287</v>
       </c>
       <c r="C49" t="n">
-        <v>-0</v>
+        <v>-0.0535</v>
       </c>
       <c r="D49" t="n">
         <v>-0.4734</v>
@@ -2707,7 +2707,7 @@
         <v>-0.1664</v>
       </c>
       <c r="C50" t="n">
-        <v>-0</v>
+        <v>-0.0692</v>
       </c>
       <c r="D50" t="n">
         <v>-0.4886</v>
@@ -2753,7 +2753,7 @@
         <v>-0.1753</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4922</v>
@@ -2799,7 +2799,7 @@
         <v>-0.2411</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.1003</v>
       </c>
       <c r="D52" t="n">
         <v>-0.5188</v>
@@ -2845,7 +2845,7 @@
         <v>-0.3276</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.1362</v>
       </c>
       <c r="D53" t="n">
         <v>-0.5537</v>
@@ -2891,7 +2891,7 @@
         <v>-0.4051</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.1685</v>
       </c>
       <c r="D54" t="n">
         <v>-0.585</v>
@@ -2937,7 +2937,7 @@
         <v>-0.4263</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.1773</v>
       </c>
       <c r="D55" t="n">
         <v>-0.5936</v>
@@ -2983,7 +2983,7 @@
         <v>-0.4772</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.1984</v>
       </c>
       <c r="D56" t="n">
         <v>-0.6141</v>
@@ -3029,7 +3029,7 @@
         <v>-0.5052</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.2101</v>
       </c>
       <c r="D57" t="n">
         <v>-0.6254999999999999</v>
@@ -3075,7 +3075,7 @@
         <v>-0.5714</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.2376</v>
       </c>
       <c r="D58" t="n">
         <v>-0.6522</v>
@@ -3121,7 +3121,7 @@
         <v>-0.5822000000000001</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.2421</v>
       </c>
       <c r="D59" t="n">
         <v>-0.6566</v>
@@ -3167,7 +3167,7 @@
         <v>-0.6159</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.2561</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6702</v>
@@ -3213,7 +3213,7 @@
         <v>-0.6663</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.2771</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6905</v>
@@ -3259,7 +3259,7 @@
         <v>-0.7547</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.3138</v>
       </c>
       <c r="D62" t="n">
         <v>-0.7262</v>
@@ -3305,7 +3305,7 @@
         <v>-0.7793</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.3241</v>
       </c>
       <c r="D63" t="n">
         <v>-0.7362</v>
@@ -3351,7 +3351,7 @@
         <v>-0.7931</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.3298</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7418</v>
@@ -3397,7 +3397,7 @@
         <v>-0.8481</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.3527</v>
       </c>
       <c r="D65" t="n">
         <v>-0.764</v>
@@ -3443,7 +3443,7 @@
         <v>-0.8773</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.3648</v>
       </c>
       <c r="D66" t="n">
         <v>-0.7758</v>
@@ -3489,7 +3489,7 @@
         <v>-0.879</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.3655</v>
       </c>
       <c r="D67" t="n">
         <v>-0.7765</v>
@@ -3535,7 +3535,7 @@
         <v>-0.9704</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.4035</v>
       </c>
       <c r="D68" t="n">
         <v>-0.8134</v>
@@ -3581,7 +3581,7 @@
         <v>-0.994</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.4134</v>
       </c>
       <c r="D69" t="n">
         <v>-0.8229</v>
@@ -3627,7 +3627,7 @@
         <v>-1.0549</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.4387</v>
       </c>
       <c r="D70" t="n">
         <v>-0.8475</v>
@@ -3673,7 +3673,7 @@
         <v>-1.1356</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.4722</v>
       </c>
       <c r="D71" t="n">
         <v>-0.8801</v>
@@ -3719,7 +3719,7 @@
         <v>-1.3886</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.5775</v>
       </c>
       <c r="D72" t="n">
         <v>-0.9823</v>
@@ -3765,7 +3765,7 @@
         <v>-1.4757</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.6137</v>
       </c>
       <c r="D73" t="n">
         <v>-1.0175</v>
@@ -3811,7 +3811,7 @@
         <v>-1.4998</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.6237</v>
       </c>
       <c r="D74" t="n">
         <v>-1.0272</v>
@@ -3857,7 +3857,7 @@
         <v>-1.5258</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.6345</v>
       </c>
       <c r="D75" t="n">
         <v>-1.0378</v>
@@ -3903,7 +3903,7 @@
         <v>-1.555</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-0.6466</v>
       </c>
       <c r="D76" t="n">
         <v>-1.0495</v>
@@ -3949,7 +3949,7 @@
         <v>-1.7372</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-0.7224</v>
       </c>
       <c r="D77" t="n">
         <v>-1.1232</v>
@@ -3995,7 +3995,7 @@
         <v>-1.8468</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-0.768</v>
       </c>
       <c r="D78" t="n">
         <v>-1.1674</v>
@@ -4041,7 +4041,7 @@
         <v>-1.8714</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-0.7782</v>
       </c>
       <c r="D79" t="n">
         <v>-1.1774</v>
@@ -4087,7 +4087,7 @@
         <v>-2.7613</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.1483</v>
       </c>
       <c r="D80" t="n">
         <v>-1.5369</v>
@@ -4133,7 +4133,7 @@
         <v>-4.7641</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-1.9812</v>
       </c>
       <c r="D81" t="n">
         <v>-2.346</v>

--- a/database/event/6861/event_6861_evp_summary.xlsx
+++ b/database/event/6861/event_6861_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.7213</v>
+        <v>7.8608</v>
       </c>
       <c r="C2" t="n">
-        <v>3.2109</v>
+        <v>3.2689</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6979</v>
+        <v>2.6878</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7213</v>
+        <v>7.8608</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6269</v>
+        <v>4.7664</v>
       </c>
       <c r="G2" t="n">
         <v>3.0944</v>
       </c>
       <c r="H2" t="n">
-        <v>6.0544</v>
+        <v>6.616</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9073</v>
+        <v>5.3625</v>
       </c>
       <c r="J2" t="n">
         <v>3.0944</v>
@@ -529,7 +529,7 @@
         <v>156</v>
       </c>
       <c r="M2" t="n">
-        <v>8.0017</v>
+        <v>8.456899999999999</v>
       </c>
       <c r="N2" t="n">
         <v>323</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.4161</v>
+        <v>7.4744</v>
       </c>
       <c r="C3" t="n">
-        <v>3.084</v>
+        <v>3.1082</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5746</v>
+        <v>2.5339</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4161</v>
+        <v>7.4744</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1487</v>
+        <v>4.207</v>
       </c>
       <c r="G3" t="n">
         <v>3.2674</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2021</v>
+        <v>4.2935</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2413</v>
+        <v>4.3661</v>
       </c>
       <c r="J3" t="n">
         <v>3.2674</v>
@@ -575,7 +575,7 @@
         <v>197</v>
       </c>
       <c r="M3" t="n">
-        <v>7.508699999999999</v>
+        <v>7.6335</v>
       </c>
       <c r="N3" t="n">
         <v>365</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6316</v>
+        <v>5.6157</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3419</v>
+        <v>2.3353</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8537</v>
+        <v>1.7934</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6316</v>
+        <v>5.6157</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1408</v>
+        <v>2.1249</v>
       </c>
       <c r="G4" t="n">
         <v>3.4908</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1408</v>
+        <v>2.1249</v>
       </c>
       <c r="I4" t="n">
         <v>2.1608</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8344</v>
+        <v>4.8558</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0104</v>
+        <v>2.0193</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5316</v>
+        <v>1.4906</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8344</v>
+        <v>4.8558</v>
       </c>
       <c r="F5" t="n">
-        <v>4.1367</v>
+        <v>4.1581</v>
       </c>
       <c r="G5" t="n">
         <v>0.6977</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1833</v>
+        <v>4.2168</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2027</v>
+        <v>4.2523</v>
       </c>
       <c r="J5" t="n">
         <v>0.6977</v>
@@ -667,7 +667,7 @@
         <v>67</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9004</v>
+        <v>4.95</v>
       </c>
       <c r="N5" t="n">
         <v>243</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8181</v>
+        <v>4.8434</v>
       </c>
       <c r="C6" t="n">
-        <v>2.0036</v>
+        <v>2.0141</v>
       </c>
       <c r="D6" t="n">
-        <v>1.525</v>
+        <v>1.4857</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8181</v>
+        <v>4.8434</v>
       </c>
       <c r="F6" t="n">
-        <v>4.1685</v>
+        <v>4.1938</v>
       </c>
       <c r="G6" t="n">
         <v>0.6496</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2103</v>
+        <v>4.3122</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4125</v>
+        <v>3.4951</v>
       </c>
       <c r="J6" t="n">
         <v>0.6496</v>
@@ -713,7 +713,7 @@
         <v>79</v>
       </c>
       <c r="M6" t="n">
-        <v>4.0621</v>
+        <v>4.1447</v>
       </c>
       <c r="N6" t="n">
         <v>197</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.785</v>
+        <v>4.774</v>
       </c>
       <c r="C7" t="n">
-        <v>1.9898</v>
+        <v>1.9853</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5117</v>
+        <v>1.4581</v>
       </c>
       <c r="E7" t="n">
-        <v>4.785</v>
+        <v>4.774</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9721</v>
+        <v>4.3864</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8129</v>
+        <v>0.3876</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9721</v>
+        <v>5.0868</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9998</v>
+        <v>4.123</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8129</v>
+        <v>0.3876</v>
       </c>
       <c r="K7" t="n">
-        <v>212</v>
+        <v>118</v>
       </c>
       <c r="L7" t="n">
-        <v>183</v>
+        <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>4.8127</v>
+        <v>4.5106</v>
       </c>
       <c r="N7" t="n">
-        <v>395</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.7623</v>
+        <v>4.7629</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9804</v>
+        <v>1.9807</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5025</v>
+        <v>1.4536</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7623</v>
+        <v>4.7629</v>
       </c>
       <c r="F8" t="n">
-        <v>4.3747</v>
+        <v>2.95</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3876</v>
+        <v>1.8129</v>
       </c>
       <c r="H8" t="n">
-        <v>5.0397</v>
+        <v>2.95</v>
       </c>
       <c r="I8" t="n">
-        <v>4.0848</v>
+        <v>2.9998</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3876</v>
+        <v>1.8129</v>
       </c>
       <c r="K8" t="n">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="L8" t="n">
-        <v>79</v>
+        <v>183</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4724</v>
+        <v>4.8127</v>
       </c>
       <c r="N8" t="n">
-        <v>197</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -824,7 +824,7 @@
         <v>1.9389</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4621</v>
+        <v>1.4136</v>
       </c>
       <c r="E9" t="n">
         <v>4.6624</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.2131</v>
+        <v>4.1962</v>
       </c>
       <c r="C10" t="n">
-        <v>1.752</v>
+        <v>1.745</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2806</v>
+        <v>1.2279</v>
       </c>
       <c r="E10" t="n">
-        <v>4.2131</v>
+        <v>4.1962</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2668</v>
+        <v>2.2499</v>
       </c>
       <c r="G10" t="n">
         <v>1.9463</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2668</v>
+        <v>2.2499</v>
       </c>
       <c r="I10" t="n">
         <v>2.2879</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6409</v>
+        <v>4.0633</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5141</v>
+        <v>1.6897</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0495</v>
+        <v>1.1749</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6409</v>
+        <v>4.0633</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4009</v>
+        <v>4.2686</v>
       </c>
       <c r="G11" t="n">
-        <v>3.24</v>
+        <v>-0.2053</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4009</v>
+        <v>4.3902</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4046</v>
+        <v>4.4644</v>
       </c>
       <c r="J11" t="n">
-        <v>3.24</v>
+        <v>-0.2053</v>
       </c>
       <c r="K11" t="n">
-        <v>212</v>
+        <v>168</v>
       </c>
       <c r="L11" t="n">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6446</v>
+        <v>4.2591</v>
       </c>
       <c r="N11" t="n">
-        <v>395</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6122</v>
+        <v>3.9076</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5021</v>
+        <v>1.625</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0379</v>
+        <v>1.1129</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6122</v>
+        <v>3.9076</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8175</v>
+        <v>3.9076</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8175</v>
+        <v>3.9076</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8531</v>
+        <v>3.9404</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>168</v>
+        <v>212</v>
       </c>
       <c r="L12" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6478</v>
+        <v>3.9404</v>
       </c>
       <c r="N12" t="n">
-        <v>365</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.5917</v>
+        <v>3.6505</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4936</v>
+        <v>1.5181</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0296</v>
+        <v>1.0104</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5917</v>
+        <v>3.6505</v>
       </c>
       <c r="F13" t="n">
-        <v>4.4468</v>
+        <v>4.5056</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8551</v>
       </c>
       <c r="H13" t="n">
-        <v>5.3299</v>
+        <v>5.5667</v>
       </c>
       <c r="I13" t="n">
-        <v>4.32</v>
+        <v>4.5119</v>
       </c>
       <c r="J13" t="n">
         <v>-0.8551</v>
@@ -1035,7 +1035,7 @@
         <v>79</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4649</v>
+        <v>3.6568</v>
       </c>
       <c r="N13" t="n">
         <v>197</v>
@@ -1044,139 +1044,139 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.3281</v>
+        <v>3.6379</v>
       </c>
       <c r="C14" t="n">
-        <v>1.384</v>
+        <v>1.5128</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9231</v>
+        <v>1.0054</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3281</v>
+        <v>3.6379</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3281</v>
+        <v>0.3979</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3281</v>
+        <v>0.3979</v>
       </c>
       <c r="I14" t="n">
-        <v>3.3436</v>
+        <v>0.4046</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="K14" t="n">
         <v>212</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3436</v>
+        <v>3.6446</v>
       </c>
       <c r="N14" t="n">
-        <v>212</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.113</v>
+        <v>3.5979</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2945</v>
+        <v>1.4962</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.9895</v>
       </c>
       <c r="E15" t="n">
-        <v>3.113</v>
+        <v>3.5979</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4445</v>
+        <v>3.2645</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3315</v>
+        <v>0.3334</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4445</v>
+        <v>3.2645</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7918</v>
+        <v>3.3197</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3315</v>
+        <v>0.3334</v>
       </c>
       <c r="K15" t="n">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="L15" t="n">
-        <v>79</v>
+        <v>183</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4603</v>
+        <v>3.6531</v>
       </c>
       <c r="N15" t="n">
-        <v>197</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.1101</v>
+        <v>3.113</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2933</v>
+        <v>1.2945</v>
       </c>
       <c r="D16" t="n">
-        <v>0.835</v>
+        <v>0.7963</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1101</v>
+        <v>3.113</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7767</v>
+        <v>3.4445</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3334</v>
+        <v>-0.3315</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7767</v>
+        <v>3.4445</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8026</v>
+        <v>2.7918</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3334</v>
+        <v>-0.3315</v>
       </c>
       <c r="K16" t="n">
-        <v>212</v>
+        <v>118</v>
       </c>
       <c r="L16" t="n">
-        <v>183</v>
+        <v>79</v>
       </c>
       <c r="M16" t="n">
-        <v>3.136</v>
+        <v>2.4603</v>
       </c>
       <c r="N16" t="n">
-        <v>395</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.5503</v>
+        <v>2.8873</v>
       </c>
       <c r="C17" t="n">
-        <v>1.0605</v>
+        <v>1.2007</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6089</v>
+        <v>0.7064</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5503</v>
+        <v>2.8873</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5503</v>
+        <v>2.8873</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5503</v>
+        <v>2.8873</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5621</v>
+        <v>2.9116</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.5621</v>
+        <v>2.9116</v>
       </c>
       <c r="N17" t="n">
         <v>212</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3773</v>
+        <v>2.3844</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9886</v>
+        <v>0.9916</v>
       </c>
       <c r="D18" t="n">
-        <v>0.539</v>
+        <v>0.506</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3773</v>
+        <v>2.3844</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1905</v>
+        <v>2.1976</v>
       </c>
       <c r="G18" t="n">
         <v>0.1868</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1905</v>
+        <v>2.1976</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1905</v>
+        <v>2.1976</v>
       </c>
       <c r="J18" t="n">
         <v>0.1868</v>
@@ -1265,7 +1265,7 @@
         <v>78</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3773</v>
+        <v>2.3844</v>
       </c>
       <c r="N18" t="n">
         <v>187</v>
@@ -1284,7 +1284,7 @@
         <v>0.9691</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5201</v>
+        <v>0.4845</v>
       </c>
       <c r="E19" t="n">
         <v>2.3304</v>
@@ -1330,7 +1330,7 @@
         <v>0.9278999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.48</v>
+        <v>0.445</v>
       </c>
       <c r="E20" t="n">
         <v>2.2313</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.1796</v>
+        <v>2.1735</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9064</v>
+        <v>0.9039</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4591</v>
+        <v>0.422</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1796</v>
+        <v>2.1735</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9399</v>
+        <v>1.9338</v>
       </c>
       <c r="G21" t="n">
         <v>0.2397</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9399</v>
+        <v>1.9338</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9489</v>
+        <v>1.9501</v>
       </c>
       <c r="J21" t="n">
         <v>0.2397</v>
@@ -1403,7 +1403,7 @@
         <v>67</v>
       </c>
       <c r="M21" t="n">
-        <v>2.1886</v>
+        <v>2.1898</v>
       </c>
       <c r="N21" t="n">
         <v>243</v>
@@ -1422,7 +1422,7 @@
         <v>0.8977000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4507</v>
+        <v>0.4162</v>
       </c>
       <c r="E22" t="n">
         <v>2.1588</v>
@@ -1458,139 +1458,139 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.083</v>
+        <v>2.085</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8662</v>
+        <v>0.867</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4201</v>
+        <v>0.3868</v>
       </c>
       <c r="E23" t="n">
-        <v>2.083</v>
+        <v>2.085</v>
       </c>
       <c r="F23" t="n">
-        <v>2.083</v>
+        <v>2.085</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.083</v>
+        <v>2.085</v>
       </c>
       <c r="I23" t="n">
-        <v>2.083</v>
+        <v>2.085</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.083</v>
+        <v>2.085</v>
       </c>
       <c r="N23" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.0321</v>
+        <v>2.083</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8451</v>
+        <v>0.8662</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3996</v>
+        <v>0.386</v>
       </c>
       <c r="E24" t="n">
-        <v>2.0321</v>
+        <v>2.083</v>
       </c>
       <c r="F24" t="n">
-        <v>2.0321</v>
+        <v>2.083</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.0321</v>
+        <v>2.083</v>
       </c>
       <c r="I24" t="n">
-        <v>2.0321</v>
+        <v>2.083</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.0321</v>
+        <v>2.083</v>
       </c>
       <c r="N24" t="n">
-        <v>115</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.9797</v>
+        <v>2.0321</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8233</v>
+        <v>0.8451</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3784</v>
+        <v>0.3657</v>
       </c>
       <c r="E25" t="n">
-        <v>1.9797</v>
+        <v>2.0321</v>
       </c>
       <c r="F25" t="n">
-        <v>1.9797</v>
+        <v>2.0321</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.9797</v>
+        <v>2.0321</v>
       </c>
       <c r="I25" t="n">
-        <v>1.9797</v>
+        <v>2.0321</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>186</v>
+        <v>115</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.9797</v>
+        <v>2.0321</v>
       </c>
       <c r="N25" t="n">
-        <v>186</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26">
@@ -1606,7 +1606,7 @@
         <v>0.7798</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3362</v>
+        <v>0.3032</v>
       </c>
       <c r="E26" t="n">
         <v>1.8752</v>
@@ -1642,357 +1642,357 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7877</v>
+        <v>1.8502</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.7694</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3008</v>
+        <v>0.2932</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7877</v>
+        <v>1.8502</v>
       </c>
       <c r="F27" t="n">
-        <v>1.5317</v>
+        <v>2.3738</v>
       </c>
       <c r="G27" t="n">
-        <v>0.256</v>
+        <v>-0.5236</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5317</v>
+        <v>2.3738</v>
       </c>
       <c r="I27" t="n">
-        <v>1.546</v>
+        <v>2.3738</v>
       </c>
       <c r="J27" t="n">
-        <v>0.256</v>
+        <v>-0.5236</v>
       </c>
       <c r="K27" t="n">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="L27" t="n">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="M27" t="n">
-        <v>1.802</v>
+        <v>1.8502</v>
       </c>
       <c r="N27" t="n">
-        <v>365</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.7245</v>
+        <v>1.7763</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7171</v>
+        <v>0.7387</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2753</v>
+        <v>0.2638</v>
       </c>
       <c r="E28" t="n">
-        <v>1.7245</v>
+        <v>1.7763</v>
       </c>
       <c r="F28" t="n">
-        <v>1.7245</v>
+        <v>1.5203</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.256</v>
       </c>
       <c r="H28" t="n">
-        <v>1.7245</v>
+        <v>1.5203</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7245</v>
+        <v>1.546</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.256</v>
       </c>
       <c r="K28" t="n">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="M28" t="n">
-        <v>1.7245</v>
+        <v>1.802</v>
       </c>
       <c r="N28" t="n">
-        <v>178</v>
+        <v>365</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.6568</v>
+        <v>1.7245</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.7171</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2479</v>
+        <v>0.2431</v>
       </c>
       <c r="E29" t="n">
-        <v>1.6568</v>
+        <v>1.7245</v>
       </c>
       <c r="F29" t="n">
-        <v>1.6568</v>
+        <v>1.7245</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.6568</v>
+        <v>1.7245</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6568</v>
+        <v>1.7245</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.6568</v>
+        <v>1.7245</v>
       </c>
       <c r="N29" t="n">
-        <v>152</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.4771</v>
+        <v>1.6568</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6143</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1754</v>
+        <v>0.2162</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4771</v>
+        <v>1.6568</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4771</v>
+        <v>1.6568</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4771</v>
+        <v>1.6568</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4771</v>
+        <v>1.6568</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4771</v>
+        <v>1.6568</v>
       </c>
       <c r="N30" t="n">
-        <v>178</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.2841</v>
+        <v>1.4771</v>
       </c>
       <c r="C31" t="n">
-        <v>0.534</v>
+        <v>0.6143</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0974</v>
+        <v>0.1446</v>
       </c>
       <c r="E31" t="n">
-        <v>1.2841</v>
+        <v>1.4771</v>
       </c>
       <c r="F31" t="n">
-        <v>1.8878</v>
+        <v>1.4771</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.6037</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.8878</v>
+        <v>1.4771</v>
       </c>
       <c r="I31" t="n">
-        <v>1.5301</v>
+        <v>1.4771</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.6037</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="L31" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9264</v>
+        <v>1.4771</v>
       </c>
       <c r="N31" t="n">
-        <v>323</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.2418</v>
+        <v>1.3352</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5164</v>
+        <v>0.5552</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0803</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>1.2418</v>
+        <v>1.3352</v>
       </c>
       <c r="F32" t="n">
-        <v>1.2418</v>
+        <v>1.9389</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.6037</v>
       </c>
       <c r="H32" t="n">
-        <v>1.2418</v>
+        <v>1.9389</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2418</v>
+        <v>1.5715</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.6037</v>
       </c>
       <c r="K32" t="n">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M32" t="n">
-        <v>1.2418</v>
+        <v>0.9677999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>152</v>
+        <v>323</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1082</v>
+        <v>1.2418</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4608</v>
+        <v>0.5164</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0263</v>
+        <v>0.0508</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1082</v>
+        <v>1.2418</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6308</v>
+        <v>1.2418</v>
       </c>
       <c r="G33" t="n">
-        <v>1.739</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6308</v>
+        <v>1.2418</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5113</v>
+        <v>1.2418</v>
       </c>
       <c r="J33" t="n">
-        <v>1.739</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="L33" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.2277</v>
+        <v>1.2418</v>
       </c>
       <c r="N33" t="n">
-        <v>323</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dycha</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9861</v>
+        <v>1.1082</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4101</v>
+        <v>0.4608</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.023</v>
+        <v>-0.0024</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9861</v>
+        <v>1.1082</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1826</v>
+        <v>-0.6308</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.1965</v>
+        <v>1.739</v>
       </c>
       <c r="H34" t="n">
-        <v>1.1826</v>
+        <v>-0.6308</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9585</v>
+        <v>-0.5113</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.1965</v>
+        <v>1.739</v>
       </c>
       <c r="K34" t="n">
         <v>167</v>
@@ -2001,7 +2001,7 @@
         <v>156</v>
       </c>
       <c r="M34" t="n">
-        <v>0.762</v>
+        <v>1.2277</v>
       </c>
       <c r="N34" t="n">
         <v>323</v>
@@ -2010,139 +2010,139 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9725</v>
+        <v>1.0782</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4044</v>
+        <v>0.4484</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0285</v>
+        <v>-0.0144</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9725</v>
+        <v>1.0782</v>
       </c>
       <c r="F35" t="n">
-        <v>1.4961</v>
+        <v>1.0782</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.5236</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.4961</v>
+        <v>1.0782</v>
       </c>
       <c r="I35" t="n">
-        <v>1.4961</v>
+        <v>1.0782</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.5236</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L35" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9725</v>
+        <v>1.0782</v>
       </c>
       <c r="N35" t="n">
-        <v>187</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>dycha</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9663</v>
+        <v>1.0025</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4018</v>
+        <v>0.4169</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.031</v>
+        <v>-0.0445</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9663</v>
+        <v>1.0025</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9663</v>
+        <v>1.199</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.1965</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9663</v>
+        <v>1.199</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9663</v>
+        <v>0.9718</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.1965</v>
       </c>
       <c r="K36" t="n">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9663</v>
+        <v>0.7753</v>
       </c>
       <c r="N36" t="n">
-        <v>152</v>
+        <v>323</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8711</v>
+        <v>0.9663</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3622</v>
+        <v>0.4018</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0589</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8711</v>
+        <v>0.9663</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8711</v>
+        <v>0.9663</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8711</v>
+        <v>0.9663</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8711</v>
+        <v>0.9663</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8711</v>
+        <v>0.9663</v>
       </c>
       <c r="N37" t="n">
-        <v>107</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5088</v>
+        <v>0.7396</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2116</v>
+        <v>0.3076</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2158</v>
+        <v>-0.1493</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5088</v>
+        <v>0.7396</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5088</v>
+        <v>0.7396</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5088</v>
+        <v>0.7396</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5112</v>
+        <v>0.7458</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5112</v>
+        <v>0.7458</v>
       </c>
       <c r="N38" t="n">
         <v>212</v>
@@ -2204,7 +2204,7 @@
         <v>0.2112</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2162</v>
+        <v>-0.2416</v>
       </c>
       <c r="E39" t="n">
         <v>0.5079</v>
@@ -2250,7 +2250,7 @@
         <v>0.2067</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2205</v>
+        <v>-0.2459</v>
       </c>
       <c r="E40" t="n">
         <v>0.4971</v>
@@ -2296,7 +2296,7 @@
         <v>0.1862</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2405</v>
+        <v>-0.2655</v>
       </c>
       <c r="E41" t="n">
         <v>0.4477</v>
@@ -2342,7 +2342,7 @@
         <v>0.1663</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2598</v>
+        <v>-0.2846</v>
       </c>
       <c r="E42" t="n">
         <v>0.3999</v>
@@ -2388,7 +2388,7 @@
         <v>0.1059</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3185</v>
+        <v>-0.3425</v>
       </c>
       <c r="E43" t="n">
         <v>0.2546</v>
@@ -2434,7 +2434,7 @@
         <v>0.0946</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3295</v>
+        <v>-0.3533</v>
       </c>
       <c r="E44" t="n">
         <v>0.2274</v>
@@ -2480,7 +2480,7 @@
         <v>0.0883</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3356</v>
+        <v>-0.3593</v>
       </c>
       <c r="E45" t="n">
         <v>0.2123</v>
@@ -2526,7 +2526,7 @@
         <v>0.0843</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3395</v>
+        <v>-0.3632</v>
       </c>
       <c r="E46" t="n">
         <v>0.2026</v>
@@ -2562,78 +2562,78 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.0382</v>
+        <v>-0.0298</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0159</v>
+        <v>-0.0124</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4368</v>
+        <v>-0.4558</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0382</v>
+        <v>-0.0298</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0382</v>
+        <v>0.9702</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0382</v>
+        <v>0.9702</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0382</v>
+        <v>0.9702</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K47" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.0382</v>
+        <v>-0.02980000000000005</v>
       </c>
       <c r="N47" t="n">
-        <v>108</v>
+        <v>187</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FASHR</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.1054</v>
+        <v>-0.0382</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0438</v>
+        <v>-0.0159</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4639</v>
+        <v>-0.4591</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.1054</v>
+        <v>-0.0382</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.1054</v>
+        <v>-0.0382</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.1054</v>
+        <v>-0.0382</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1054</v>
+        <v>-0.0382</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1054</v>
+        <v>-0.0382</v>
       </c>
       <c r="N48" t="n">
         <v>108</v>
@@ -2654,676 +2654,676 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.1287</v>
+        <v>-0.0509</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0535</v>
+        <v>-0.0212</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4734</v>
+        <v>-0.4642</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.1287</v>
+        <v>-0.0509</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.1287</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1287</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1293</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K49" t="n">
-        <v>212</v>
+        <v>109</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.1293</v>
+        <v>-0.05089999999999995</v>
       </c>
       <c r="N49" t="n">
-        <v>212</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>FASHR</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1664</v>
+        <v>-0.1054</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0692</v>
+        <v>-0.0438</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4886</v>
+        <v>-0.4859</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1664</v>
+        <v>-0.1054</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8336</v>
+        <v>-0.1054</v>
       </c>
       <c r="G50" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8336</v>
+        <v>-0.1054</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8336</v>
+        <v>-0.1054</v>
       </c>
       <c r="J50" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L50" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1664</v>
+        <v>-0.1054</v>
       </c>
       <c r="N50" t="n">
-        <v>187</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FaNg</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1753</v>
+        <v>-0.1282</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0533</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4922</v>
+        <v>-0.495</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1753</v>
+        <v>-0.1282</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1753</v>
+        <v>-0.1282</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1753</v>
+        <v>-0.1282</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1753</v>
+        <v>-0.1293</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>152</v>
+        <v>212</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1753</v>
+        <v>-0.1293</v>
       </c>
       <c r="N51" t="n">
-        <v>152</v>
+        <v>212</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>FaNg</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2411</v>
+        <v>-0.1753</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1003</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5188</v>
+        <v>-0.5137</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.2411</v>
+        <v>-0.1753</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.1753</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5155</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.1753</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.7637</v>
+        <v>-0.1753</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5155</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="L52" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.2482000000000001</v>
+        <v>-0.1753</v>
       </c>
       <c r="N52" t="n">
-        <v>365</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3276</v>
+        <v>-0.2355</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1362</v>
+        <v>-0.0979</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5537</v>
+        <v>-0.5377</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.3276</v>
+        <v>-0.2355</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3276</v>
+        <v>-0.751</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>0.5155</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.3276</v>
+        <v>-0.751</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3276</v>
+        <v>-0.7637</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>0.5155</v>
       </c>
       <c r="K53" t="n">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.3276</v>
+        <v>-0.2482000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>178</v>
+        <v>365</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.4051</v>
+        <v>-0.2819</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1685</v>
+        <v>-0.1172</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.585</v>
+        <v>-0.5562</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.4051</v>
+        <v>-0.2819</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.4051</v>
+        <v>-0.2819</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.4051</v>
+        <v>-0.2819</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.4051</v>
+        <v>-0.2843</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.4051</v>
+        <v>-0.2843</v>
       </c>
       <c r="N54" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>F1KU</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.4263</v>
+        <v>-0.3276</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1773</v>
+        <v>-0.1362</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5936</v>
+        <v>-0.5744</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.4263</v>
+        <v>-0.3276</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.4263</v>
+        <v>-0.3276</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.4263</v>
+        <v>-0.3276</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4263</v>
+        <v>-0.3276</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.4263</v>
+        <v>-0.3276</v>
       </c>
       <c r="N55" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>wiz</t>
+          <t>Altekz</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.4772</v>
+        <v>-0.3785</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1984</v>
+        <v>-0.1574</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6141</v>
+        <v>-0.5947</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.4772</v>
+        <v>-0.3785</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.4772</v>
+        <v>-0.1656</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>-0.2129</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.4772</v>
+        <v>-0.1656</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4772</v>
+        <v>-0.167</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>-0.2129</v>
       </c>
       <c r="K56" t="n">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.4772</v>
+        <v>-0.3799</v>
       </c>
       <c r="N56" t="n">
-        <v>90</v>
+        <v>243</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Altekz</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.5052</v>
+        <v>-0.4051</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2101</v>
+        <v>-0.1685</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.5052</v>
+        <v>-0.4051</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2923</v>
+        <v>-0.4051</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.2129</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2923</v>
+        <v>-0.4051</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2936</v>
+        <v>-0.4051</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.2129</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>176</v>
+        <v>115</v>
       </c>
       <c r="L57" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.5065000000000001</v>
+        <v>-0.4051</v>
       </c>
       <c r="N57" t="n">
-        <v>243</v>
+        <v>115</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>F1KU</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.5714</v>
+        <v>-0.4263</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2376</v>
+        <v>-0.1773</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6522</v>
+        <v>-0.6137</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.5714</v>
+        <v>-0.4263</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.5714</v>
+        <v>-0.4263</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.5714</v>
+        <v>-0.4263</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.5714</v>
+        <v>-0.4263</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.5714</v>
+        <v>-0.4263</v>
       </c>
       <c r="N58" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Bwills</t>
+          <t>wiz</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.4772</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2421</v>
+        <v>-0.1984</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6566</v>
+        <v>-0.634</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.4772</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.4772</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.4772</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.4772</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.4772</v>
       </c>
       <c r="N59" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.6159</v>
+        <v>-0.5714</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2561</v>
+        <v>-0.2376</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6702</v>
+        <v>-0.6716</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.6159</v>
+        <v>-0.5714</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.6159</v>
+        <v>-0.5714</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.6159</v>
+        <v>-0.5714</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.6159</v>
+        <v>-0.5714</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.6159</v>
+        <v>-0.5714</v>
       </c>
       <c r="N60" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>Bwills</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.6663</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2771</v>
+        <v>-0.2421</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6905</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.6663</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.6663</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.6663</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6694</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>212</v>
+        <v>60</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.6694</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="N61" t="n">
-        <v>212</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.7547</v>
+        <v>-0.6159</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3138</v>
+        <v>-0.2561</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7262</v>
+        <v>-0.6893</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.7547</v>
+        <v>-0.6159</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.7547</v>
+        <v>-0.6159</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.7547</v>
+        <v>-0.6159</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.7547</v>
+        <v>-0.6159</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.7547</v>
+        <v>-0.6159</v>
       </c>
       <c r="N62" t="n">
-        <v>90</v>
+        <v>152</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>neaLaN</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.7793</v>
+        <v>-0.7547</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3241</v>
+        <v>-0.3138</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7362</v>
+        <v>-0.7446</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.7793</v>
+        <v>-0.7547</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.7793</v>
+        <v>-0.7547</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.7793</v>
+        <v>-0.7547</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.7793</v>
+        <v>-0.7547</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.7793</v>
+        <v>-0.7547</v>
       </c>
       <c r="N63" t="n">
         <v>90</v>
@@ -3344,185 +3344,185 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>cynic</t>
+          <t>neaLaN</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.7931</v>
+        <v>-0.7793</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.3298</v>
+        <v>-0.3241</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7418</v>
+        <v>-0.7544</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.7931</v>
+        <v>-0.7793</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.7931</v>
+        <v>-0.7793</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.7931</v>
+        <v>-0.7793</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.7931</v>
+        <v>-0.7793</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.7931</v>
+        <v>-0.7793</v>
       </c>
       <c r="N64" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NEOFRAG</t>
+          <t>cynic</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8481</v>
+        <v>-0.7931</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3527</v>
+        <v>-0.3298</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.764</v>
+        <v>-0.7599</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.8481</v>
+        <v>-0.7931</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8481</v>
+        <v>-0.7931</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8481</v>
+        <v>-0.7931</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.8481</v>
+        <v>-0.7931</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>186</v>
+        <v>60</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.8481</v>
+        <v>-0.7931</v>
       </c>
       <c r="N65" t="n">
-        <v>186</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>NEOFRAG</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.8773</v>
+        <v>-0.8481</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3648</v>
+        <v>-0.3527</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7758</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.8773</v>
+        <v>-0.8481</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.8773</v>
+        <v>-0.8481</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.8773</v>
+        <v>-0.8481</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8773</v>
+        <v>-0.8481</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>60</v>
+        <v>186</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.8773</v>
+        <v>-0.8481</v>
       </c>
       <c r="N66" t="n">
-        <v>60</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.879</v>
+        <v>-0.8773</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.3655</v>
+        <v>-0.3648</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7765</v>
+        <v>-0.7934</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.879</v>
+        <v>-0.8773</v>
       </c>
       <c r="F67" t="n">
-        <v>0.121</v>
+        <v>-0.8773</v>
       </c>
       <c r="G67" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.121</v>
+        <v>-0.8773</v>
       </c>
       <c r="I67" t="n">
-        <v>0.121</v>
+        <v>-0.8773</v>
       </c>
       <c r="J67" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="L67" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.879</v>
+        <v>-0.8773</v>
       </c>
       <c r="N67" t="n">
-        <v>187</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68">
@@ -3538,7 +3538,7 @@
         <v>-0.4035</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8134</v>
+        <v>-0.8305</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9704</v>
@@ -3584,7 +3584,7 @@
         <v>-0.4134</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8229</v>
+        <v>-0.8399</v>
       </c>
       <c r="E69" t="n">
         <v>-0.994</v>
@@ -3630,7 +3630,7 @@
         <v>-0.4387</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8475</v>
+        <v>-0.8642</v>
       </c>
       <c r="E70" t="n">
         <v>-1.0549</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.1356</v>
+        <v>-1.1346</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.4722</v>
+        <v>-0.4718</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8801</v>
+        <v>-0.8959</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.1356</v>
+        <v>-1.1346</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.2644</v>
+        <v>-0.2634</v>
       </c>
       <c r="G71" t="n">
         <v>-0.8712</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.2644</v>
+        <v>-0.2634</v>
       </c>
       <c r="I71" t="n">
         <v>-0.2656</v>
@@ -3722,7 +3722,7 @@
         <v>-0.5775</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9823</v>
+        <v>-0.9971</v>
       </c>
       <c r="E72" t="n">
         <v>-1.3886</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.4757</v>
+        <v>-1.4739</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.6137</v>
+        <v>-0.6129</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0175</v>
+        <v>-1.0311</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.4757</v>
+        <v>-1.4739</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.4757</v>
+        <v>-0.4739</v>
       </c>
       <c r="G73" t="n">
         <v>-1</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.4757</v>
+        <v>-0.4739</v>
       </c>
       <c r="I73" t="n">
         <v>-0.4779</v>
@@ -3814,7 +3814,7 @@
         <v>-0.6237</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0272</v>
+        <v>-1.0414</v>
       </c>
       <c r="E74" t="n">
         <v>-1.4998</v>
@@ -3860,7 +3860,7 @@
         <v>-0.6345</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0378</v>
+        <v>-1.0518</v>
       </c>
       <c r="E75" t="n">
         <v>-1.5258</v>
@@ -3906,7 +3906,7 @@
         <v>-0.6466</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0495</v>
+        <v>-1.0634</v>
       </c>
       <c r="E76" t="n">
         <v>-1.555</v>
@@ -3952,7 +3952,7 @@
         <v>-0.7224</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1232</v>
+        <v>-1.136</v>
       </c>
       <c r="E77" t="n">
         <v>-1.7372</v>
@@ -3998,7 +3998,7 @@
         <v>-0.768</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1674</v>
+        <v>-1.1797</v>
       </c>
       <c r="E78" t="n">
         <v>-1.8468</v>
@@ -4044,7 +4044,7 @@
         <v>-0.7782</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1774</v>
+        <v>-1.1895</v>
       </c>
       <c r="E79" t="n">
         <v>-1.8714</v>
@@ -4090,7 +4090,7 @@
         <v>-1.1483</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.5369</v>
+        <v>-1.544</v>
       </c>
       <c r="E80" t="n">
         <v>-2.7613</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4.7641</v>
+        <v>-4.7433</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.9812</v>
+        <v>-1.9725</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.346</v>
+        <v>-2.3336</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.7641</v>
+        <v>-4.7433</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.7888</v>
+        <v>-2.768</v>
       </c>
       <c r="G81" t="n">
         <v>-1.9753</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.7888</v>
+        <v>-2.768</v>
       </c>
       <c r="I81" t="n">
         <v>-2.8148</v>
